--- a/E/RPROCL3.xlsx
+++ b/E/RPROCL3.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
   <si>
     <t/>
   </si>
   <si>
-    <t>10037632</t>
-  </si>
-  <si>
-    <t>WALL'S FEAST CKLT.65</t>
+    <t>20138475</t>
+  </si>
+  <si>
+    <t>WALLS MGNUM STRW PAN</t>
   </si>
   <si>
     <t>RPROCL3</t>
@@ -28,28 +28,10 @@
     <t>8</t>
   </si>
   <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>10037640</t>
-  </si>
-  <si>
-    <t>WALL'S FEAST VNILA65</t>
-  </si>
-  <si>
-    <t>54</t>
-  </si>
-  <si>
-    <t>20070539</t>
-  </si>
-  <si>
-    <t>AICE CHOCO CRPSY 60G</t>
-  </si>
-  <si>
-    <t>68</t>
+    <t>37</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
   </si>
 </sst>
 </file>
@@ -442,7 +424,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -492,46 +474,6 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
